--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484554_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484554_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.9692</v>
+        <v>5.4064</v>
       </c>
       <c r="E2" t="n">
-        <v>2.3298</v>
+        <v>2.7423</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6393</v>
+        <v>2.6641</v>
       </c>
       <c r="G2" t="n">
         <v>4.4503</v>
@@ -610,13 +610,13 @@
         <v>3.2986</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4743</v>
+        <v>0.9116</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3273</v>
+        <v>0.7398</v>
       </c>
       <c r="U2" t="n">
-        <v>0.147</v>
+        <v>0.1717</v>
       </c>
       <c r="V2" t="n">
         <v>-0.3219</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.8615</v>
+        <v>4.6972</v>
       </c>
       <c r="E3" t="n">
-        <v>3.8012</v>
+        <v>4.4882</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0603</v>
+        <v>0.209</v>
       </c>
       <c r="G3" t="n">
         <v>3.2496</v>
@@ -688,13 +688,13 @@
         <v>1.0995</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3044</v>
+        <v>0.5313</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4774</v>
+        <v>0.2097</v>
       </c>
       <c r="U3" t="n">
-        <v>0.173</v>
+        <v>0.3216</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9542</v>
+        <v>3.1881</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6618000000000001</v>
+        <v>0.7719</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2924</v>
+        <v>2.4162</v>
       </c>
       <c r="G4" t="n">
         <v>0.6708</v>
@@ -766,13 +766,13 @@
         <v>3.1154</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0268</v>
+        <v>0.2608</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0347</v>
+        <v>0.1448</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.1159</v>
       </c>
       <c r="V4" t="n">
         <v>1.89</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. MONDRAGON VIDAL</t>
+          <t>P. ROCATI ALEGRE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9299</v>
+        <v>2.8608</v>
       </c>
       <c r="E5" t="n">
-        <v>4.5914</v>
+        <v>-0.916</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.6615</v>
+        <v>3.7768</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5497</v>
+        <v>1.6813</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2799</v>
+        <v>1.3221</v>
       </c>
       <c r="I5" t="n">
-        <v>2.2698</v>
+        <v>0.3592</v>
       </c>
       <c r="J5" t="n">
-        <v>4.5725</v>
+        <v>1.0511</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2446</v>
+        <v>1.5573</v>
       </c>
       <c r="L5" t="n">
-        <v>3.3279</v>
+        <v>-0.5062</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.0228</v>
+        <v>0.6302</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9647</v>
+        <v>-0.2351</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.0581</v>
+        <v>0.8653</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3665</v>
+        <v>1.4661</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.0158</v>
+        <v>-1.8326</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6493</v>
+        <v>3.2986</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3906</v>
+        <v>0.0458</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7677</v>
+        <v>-0.1346</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6228</v>
+        <v>0.1804</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6439</v>
+        <v>-0.3324</v>
       </c>
       <c r="W5" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.9109</v>
+        <v>-0.3324</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. ROCATI ALEGRE</t>
+          <t>B. MONDRAGON VIDAL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.7725</v>
+        <v>2.7209</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.93</v>
+        <v>4.6053</v>
       </c>
       <c r="F6" t="n">
-        <v>3.7025</v>
+        <v>-1.8845</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6813</v>
+        <v>2.5497</v>
       </c>
       <c r="H6" t="n">
-        <v>1.3221</v>
+        <v>0.2799</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3592</v>
+        <v>2.2698</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0511</v>
+        <v>4.5725</v>
       </c>
       <c r="K6" t="n">
-        <v>1.5573</v>
+        <v>1.2446</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5062</v>
+        <v>3.3279</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6302</v>
+        <v>-2.0228</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2351</v>
+        <v>-0.9647</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8653</v>
+        <v>-1.0581</v>
       </c>
       <c r="P6" t="n">
-        <v>1.4661</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.8326</v>
+        <v>-2.0158</v>
       </c>
       <c r="R6" t="n">
-        <v>3.2986</v>
+        <v>1.6493</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0425</v>
+        <v>1.1816</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1485</v>
+        <v>0.7817</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1061</v>
+        <v>0.3999</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3324</v>
+        <v>-0.6439</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.3324</v>
+        <v>-1.9109</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. AZNAR MARTINEZ</t>
+          <t>K. MONTAÑO LINARES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.0786</v>
+        <v>1.5753</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2446</v>
+        <v>1.5753</v>
       </c>
       <c r="F7" t="n">
-        <v>0.834</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2529</v>
+        <v>1.5753</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3754</v>
+        <v>0.3251</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6283</v>
+        <v>1.2502</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5034</v>
+        <v>1.5753</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1891</v>
+        <v>0.3251</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6925</v>
+        <v>1.2502</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2505</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1863</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0643</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5498</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4661</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.2314</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.6471</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5843</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9554</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0104</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.9658</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. MONTAÑO LINARES</t>
+          <t>A. AZNAR MARTINEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5753</v>
+        <v>0.9739</v>
       </c>
       <c r="E8" t="n">
-        <v>1.5753</v>
+        <v>0.3381</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>0.6358</v>
       </c>
       <c r="G8" t="n">
-        <v>1.5753</v>
+        <v>0.2529</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3251</v>
+        <v>-0.3754</v>
       </c>
       <c r="I8" t="n">
-        <v>1.2502</v>
+        <v>0.6283</v>
       </c>
       <c r="J8" t="n">
-        <v>1.5753</v>
+        <v>0.5034</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3251</v>
+        <v>-0.1891</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2502</v>
+        <v>0.6925</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>-0.2505</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-0.1863</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>-0.0643</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.5498</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.4661</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.1267</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.7406</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.3861</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.9554</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.0104</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.9658</v>
       </c>
     </row>
     <row r="9">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.09379999999999999</v>
+        <v>-0.0132</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1195</v>
+        <v>0.0373</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0257</v>
+        <v>-0.0505</v>
       </c>
       <c r="G11" t="n">
         <v>0.9593</v>
@@ -1312,13 +1312,13 @@
         <v>2.7489</v>
       </c>
       <c r="S11" t="n">
-        <v>0.9171</v>
+        <v>0.8101</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4374</v>
+        <v>0.3552</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4797</v>
+        <v>0.4549</v>
       </c>
       <c r="V11" t="n">
         <v>-1.5993</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.6496</v>
+        <v>-1.1575</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.1928</v>
+        <v>-2.8492</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5431</v>
+        <v>1.6918</v>
       </c>
       <c r="G12" t="n">
         <v>-1.251</v>
@@ -1390,13 +1390,13 @@
         <v>2.5656</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.781</v>
+        <v>-0.2888</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5143</v>
+        <v>-0.1708</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2667</v>
+        <v>-0.118</v>
       </c>
       <c r="V12" t="n">
         <v>-1.267</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. MORAL SANMARTIN</t>
+          <t>J. AVINO GOMEZ-SENENT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.6044</v>
+        <v>-3.4622</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.1014</v>
+        <v>-4.4978</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5031</v>
+        <v>1.0356</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.6776</v>
+        <v>-3.8611</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.2641</v>
+        <v>-2.2104</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.4135</v>
+        <v>-1.6508</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.6729</v>
+        <v>-4.0838</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.6443</v>
+        <v>-2.369</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.0286</v>
+        <v>-1.7147</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.0047</v>
+        <v>0.2226</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.6198</v>
+        <v>0.1587</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.3849</v>
+        <v>0.064</v>
       </c>
       <c r="P13" t="n">
-        <v>1.6493</v>
+        <v>1.8326</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.0995</v>
+        <v>-0.9163</v>
       </c>
       <c r="R13" t="n">
         <v>2.7489</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3688</v>
+        <v>0.4668</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2398</v>
+        <v>0.5023</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6086</v>
+        <v>-0.0355</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.945</v>
+        <v>-1.9005</v>
       </c>
       <c r="W13" t="n">
-        <v>1.9109</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.8559</v>
+        <v>-1.9005</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. AVINO GOMEZ-SENENT</t>
+          <t>A. MORAL SANMARTIN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.9077</v>
+        <v>-3.6156</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.7451</v>
+        <v>-2.8401</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8374</v>
+        <v>-0.7756</v>
       </c>
       <c r="G14" t="n">
-        <v>-3.8611</v>
+        <v>-4.6776</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.2104</v>
+        <v>-1.2641</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.6508</v>
+        <v>-3.4135</v>
       </c>
       <c r="J14" t="n">
-        <v>-4.0838</v>
+        <v>-3.6729</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.369</v>
+        <v>-0.6443</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.7147</v>
+        <v>-3.0286</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2226</v>
+        <v>-1.0047</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1587</v>
+        <v>-0.6198</v>
       </c>
       <c r="O14" t="n">
-        <v>0.064</v>
+        <v>-0.3849</v>
       </c>
       <c r="P14" t="n">
-        <v>1.8326</v>
+        <v>1.6493</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9163</v>
+        <v>-1.0995</v>
       </c>
       <c r="R14" t="n">
         <v>2.7489</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0213</v>
+        <v>0.3576</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2549</v>
+        <v>0.0215</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2336</v>
+        <v>0.3361</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.9005</v>
+        <v>-0.945</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.9109</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.9005</v>
+        <v>-2.8559</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>13.0235</v>
+        <v>14.1243</v>
       </c>
       <c r="E15" t="n">
-        <v>3.304500000000002</v>
+        <v>4.405500000000002</v>
       </c>
       <c r="F15" t="n">
-        <v>9.7187</v>
+        <v>9.718699999999998</v>
       </c>
       <c r="G15" t="n">
         <v>6.549700000000001</v>
@@ -1600,10 +1600,10 @@
         <v>11.9863</v>
       </c>
       <c r="K15" t="n">
-        <v>5.893000000000001</v>
+        <v>5.893</v>
       </c>
       <c r="L15" t="n">
-        <v>6.093400000000003</v>
+        <v>6.093400000000002</v>
       </c>
       <c r="M15" t="n">
         <v>-5.4366</v>
@@ -1615,7 +1615,7 @@
         <v>-1.6048</v>
       </c>
       <c r="P15" t="n">
-        <v>8.246599999999999</v>
+        <v>8.246600000000001</v>
       </c>
       <c r="Q15" t="n">
         <v>-16.4932</v>
@@ -1624,13 +1624,13 @@
         <v>24.7398</v>
       </c>
       <c r="S15" t="n">
-        <v>4.3024</v>
+        <v>5.4035</v>
       </c>
       <c r="T15" t="n">
-        <v>2.0891</v>
+        <v>3.1902</v>
       </c>
       <c r="U15" t="n">
-        <v>2.2133</v>
+        <v>2.2131</v>
       </c>
       <c r="V15" t="n">
         <v>-6.0754</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.8898</v>
+        <v>4.5994</v>
       </c>
       <c r="E16" t="n">
-        <v>4.7036</v>
+        <v>4.6074</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8138</v>
+        <v>-0.008</v>
       </c>
       <c r="G16" t="n">
         <v>3.4709</v>
@@ -1702,13 +1702,13 @@
         <v>2.5656</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.2592</v>
+        <v>-0.5496</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.46</v>
+        <v>-0.5562</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7992</v>
+        <v>0.0066</v>
       </c>
       <c r="V16" t="n">
         <v>0.945</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. ARIJA DE LA PEÑA</t>
+          <t>P. ARISTA CALLAU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3251</v>
+        <v>0.8105</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3251</v>
+        <v>0.5903</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>0.2202</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3251</v>
+        <v>3.025</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3251</v>
+        <v>1.7012</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1.3237</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3251</v>
+        <v>4.3628</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3251</v>
+        <v>2.2693</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.0936</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>-1.3379</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>-0.5679999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>-0.7698</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-1.6493</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-4.5814</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.9321</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-0.586</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>-0.4789</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>-0.1071</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.0208</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.2878</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. ARIJA DE LA PENA</t>
+          <t>R. HOLGADO CUELLAR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3081</v>
+        <v>0.7417</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5531</v>
+        <v>1.1713</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8613</v>
+        <v>-0.4296</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.535</v>
+        <v>-0.6103</v>
       </c>
       <c r="H18" t="n">
-        <v>2.0873</v>
+        <v>0.0374</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.6223</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>1.0179</v>
+        <v>0.5335</v>
       </c>
       <c r="K18" t="n">
-        <v>2.7743</v>
+        <v>1.1487</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.7564</v>
+        <v>-0.6153</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.5529</v>
+        <v>-1.1437</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6870000000000001</v>
+        <v>-1.1113</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8659</v>
+        <v>-0.0324</v>
       </c>
       <c r="P18" t="n">
-        <v>-3.4819</v>
+        <v>0.1833</v>
       </c>
       <c r="Q18" t="n">
-        <v>-5.4977</v>
+        <v>-1.8326</v>
       </c>
       <c r="R18" t="n">
         <v>2.0158</v>
       </c>
       <c r="S18" t="n">
-        <v>1.4691</v>
+        <v>-0.4306</v>
       </c>
       <c r="T18" t="n">
-        <v>1.0604</v>
+        <v>-0.3959</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4088</v>
+        <v>-0.0347</v>
       </c>
       <c r="V18" t="n">
-        <v>2.8559</v>
+        <v>1.5993</v>
       </c>
       <c r="W18" t="n">
         <v>2.8663</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.0104</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. HOLGADO CUELLAR</t>
+          <t>D. ARIJA DE LA PEÑA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2198</v>
+        <v>0.3251</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5944</v>
+        <v>0.3251</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8142</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6103</v>
+        <v>0.3251</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0374</v>
+        <v>0.3251</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6477000000000001</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5335</v>
+        <v>0.3251</v>
       </c>
       <c r="K19" t="n">
-        <v>1.1487</v>
+        <v>0.3251</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6153</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.1437</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1113</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0324</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1833</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.0158</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3922</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9728</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4193</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.5993</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.8663</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. ARISTA CALLAU</t>
+          <t>D. ARIJA DE LA PENA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8679</v>
+        <v>-0.9173</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1789</v>
+        <v>-1.5147</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6889999999999999</v>
+        <v>0.5974</v>
       </c>
       <c r="G20" t="n">
-        <v>3.025</v>
+        <v>-0.535</v>
       </c>
       <c r="H20" t="n">
-        <v>1.7012</v>
+        <v>2.0873</v>
       </c>
       <c r="I20" t="n">
-        <v>1.3237</v>
+        <v>-2.6223</v>
       </c>
       <c r="J20" t="n">
-        <v>4.3628</v>
+        <v>1.0179</v>
       </c>
       <c r="K20" t="n">
-        <v>2.2693</v>
+        <v>2.7743</v>
       </c>
       <c r="L20" t="n">
-        <v>2.0936</v>
+        <v>-1.7564</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3379</v>
+        <v>-1.5529</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5679999999999999</v>
+        <v>-0.6870000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7698</v>
+        <v>-0.8659</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.6493</v>
+        <v>-3.4819</v>
       </c>
       <c r="Q20" t="n">
-        <v>-4.5814</v>
+        <v>-5.4977</v>
       </c>
       <c r="R20" t="n">
-        <v>2.9321</v>
+        <v>2.0158</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.2644</v>
+        <v>0.2438</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.2481</v>
+        <v>0.0988</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.0163</v>
+        <v>0.145</v>
       </c>
       <c r="V20" t="n">
-        <v>0.0208</v>
+        <v>2.8559</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2878</v>
+        <v>2.8663</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.267</v>
+        <v>-0.0104</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8936</v>
+        <v>-1.5512</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.903</v>
+        <v>-1.6146</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0095</v>
+        <v>0.0634</v>
       </c>
       <c r="G21" t="n">
         <v>-0.1479</v>
@@ -2092,13 +2092,13 @@
         <v>0.733</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6173999999999999</v>
+        <v>-0.2751</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3854</v>
+        <v>-0.0969</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2321</v>
+        <v>-0.1782</v>
       </c>
       <c r="V21" t="n">
         <v>-0.945</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. NEBOT GARCIA</t>
+          <t>C. FUSTER ROYO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4144</v>
+        <v>-2.8647</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.032</v>
+        <v>-3.5614</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3824</v>
+        <v>0.6968</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.7473</v>
+        <v>-3.7378</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.324</v>
+        <v>-2.6028</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.4233</v>
+        <v>-1.1351</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.1337</v>
+        <v>-2.3941</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.576</v>
+        <v>-1.8364</v>
       </c>
       <c r="L22" t="n">
         <v>-0.5577</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.6136</v>
+        <v>-1.3437</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.748</v>
+        <v>-0.7664</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8656</v>
+        <v>-0.5774</v>
       </c>
       <c r="P22" t="n">
-        <v>0.5498</v>
+        <v>-2.0158</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-4.5814</v>
       </c>
       <c r="R22" t="n">
-        <v>0.5498</v>
+        <v>2.5656</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5938</v>
+        <v>-0.9119</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2753</v>
+        <v>-0.3869</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3186</v>
+        <v>-0.5251</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.6231</v>
+        <v>3.8009</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.6231</v>
+        <v>3.8009</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E. DIAGNE</t>
+          <t>M. NEBOT GARCIA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4521</v>
+        <v>-3.2191</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.6036</v>
+        <v>-1.9359</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1515</v>
+        <v>-1.2833</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.0742</v>
+        <v>-2.7473</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.936</v>
+        <v>-1.324</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.1382</v>
+        <v>-1.4233</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.1639</v>
+        <v>-1.1337</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.7313</v>
+        <v>-0.576</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.4327</v>
+        <v>-0.5577</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.9103</v>
+        <v>-1.6136</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.2047</v>
+        <v>-0.748</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.7056</v>
+        <v>-0.8656</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.5498</v>
+        <v>0.5498</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.7489</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.1991</v>
+        <v>0.5498</v>
       </c>
       <c r="S23" t="n">
-        <v>2.3838</v>
+        <v>-0.3986</v>
       </c>
       <c r="T23" t="n">
-        <v>0.9872</v>
+        <v>-0.1791</v>
       </c>
       <c r="U23" t="n">
-        <v>1.3966</v>
+        <v>-0.2195</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.212</v>
+        <v>-0.6231</v>
       </c>
       <c r="W23" t="n">
-        <v>0.3219</v>
+        <v>-0.6231</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.5339</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C. FUSTER ROYO</t>
+          <t>D. KEITH CAMARA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.4722</v>
+        <v>-3.6115</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.5614</v>
+        <v>-3.2211</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0892</v>
+        <v>-0.3904</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.7378</v>
+        <v>-2.5184</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.6028</v>
+        <v>0.5525</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.1351</v>
+        <v>-3.0709</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.3941</v>
+        <v>-0.8618</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.8364</v>
+        <v>1.5356</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.5577</v>
+        <v>-2.3974</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.3437</v>
+        <v>-1.6566</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.7664</v>
+        <v>-0.9831</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.5774</v>
+        <v>-0.6735</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.0158</v>
+        <v>-1.8326</v>
       </c>
       <c r="Q24" t="n">
-        <v>-4.5814</v>
+        <v>-2.7489</v>
       </c>
       <c r="R24" t="n">
-        <v>2.5656</v>
+        <v>0.9163</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.5195</v>
+        <v>0.106</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3869</v>
+        <v>-0.244</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.1327</v>
+        <v>0.3499</v>
       </c>
       <c r="V24" t="n">
-        <v>3.8009</v>
+        <v>0.6335</v>
       </c>
       <c r="W24" t="n">
-        <v>3.8009</v>
+        <v>0.6335</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>D. KEITH CAMARA</t>
+          <t>E. DIAGNE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.2264</v>
+        <v>-4.7723</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.5096</v>
+        <v>-4.5652</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.7168</v>
+        <v>-0.2071</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.5184</v>
+        <v>-3.0742</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5525</v>
+        <v>-1.936</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.0709</v>
+        <v>-1.1382</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.8618</v>
+        <v>-2.1639</v>
       </c>
       <c r="K25" t="n">
-        <v>1.5356</v>
+        <v>-1.7313</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.3974</v>
+        <v>-0.4327</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.6566</v>
+        <v>-0.9103</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.9831</v>
+        <v>-0.2047</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.6735</v>
+        <v>-0.7056</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.8326</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q25" t="n">
         <v>-2.7489</v>
       </c>
       <c r="R25" t="n">
-        <v>0.9163</v>
+        <v>2.1991</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.5089</v>
+        <v>1.0637</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5324</v>
+        <v>0.0257</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0235</v>
+        <v>1.038</v>
       </c>
       <c r="V25" t="n">
-        <v>0.6335</v>
+        <v>-2.212</v>
       </c>
       <c r="W25" t="n">
-        <v>0.6335</v>
+        <v>0.3219</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-2.5339</v>
       </c>
     </row>
     <row r="26">
@@ -2437,22 +2437,22 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-13.0234</v>
+        <v>-10.4594</v>
       </c>
       <c r="E26" t="n">
-        <v>-9.718500000000001</v>
+        <v>-9.718799999999998</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.3047</v>
+        <v>-0.7406000000000001</v>
       </c>
       <c r="G26" t="n">
-        <v>-6.549900000000001</v>
+        <v>-6.5499</v>
       </c>
       <c r="H26" t="n">
-        <v>-2.061199999999999</v>
+        <v>-2.0612</v>
       </c>
       <c r="I26" t="n">
-        <v>-4.488799999999999</v>
+        <v>-4.4888</v>
       </c>
       <c r="J26" t="n">
         <v>5.436699999999999</v>
@@ -2461,7 +2461,7 @@
         <v>3.8318</v>
       </c>
       <c r="L26" t="n">
-        <v>1.6047</v>
+        <v>1.604699999999999</v>
       </c>
       <c r="M26" t="n">
         <v>-11.9864</v>
@@ -2470,7 +2470,7 @@
         <v>-5.8929</v>
       </c>
       <c r="O26" t="n">
-        <v>-6.0935</v>
+        <v>-6.093499999999999</v>
       </c>
       <c r="P26" t="n">
         <v>-8.246599999999999</v>
@@ -2482,22 +2482,22 @@
         <v>16.4931</v>
       </c>
       <c r="S26" t="n">
-        <v>-4.3025</v>
+        <v>-1.7383</v>
       </c>
       <c r="T26" t="n">
-        <v>-2.2133</v>
+        <v>-2.2134</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.0893</v>
+        <v>0.4749</v>
       </c>
       <c r="V26" t="n">
-        <v>6.075299999999999</v>
+        <v>6.0753</v>
       </c>
       <c r="W26" t="n">
         <v>11.7975</v>
       </c>
       <c r="X26" t="n">
-        <v>-5.722099999999999</v>
+        <v>-5.7221</v>
       </c>
     </row>
   </sheetData>
